--- a/MAP作成ツール.xlsx
+++ b/MAP作成ツール.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HAL\GCG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77AD46B-E1B9-4B28-AFBA-5E614650EBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B481D87E-285A-49DE-9E99-901DA4973B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2250" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="11" xr2:uid="{CC14055A-6DCF-4CBC-983C-6ED02533F1F5}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="7" xr2:uid="{CC14055A-6DCF-4CBC-983C-6ED02533F1F5}"/>
   </bookViews>
   <sheets>
     <sheet name="取説" sheetId="39" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
